--- a/result/月度汇总.xlsx
+++ b/result/月度汇总.xlsx
@@ -632,22 +632,22 @@
         <v>71.67</v>
       </c>
       <c r="E6" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="F6" t="n">
-        <v>26.22</v>
+        <v>26.23</v>
       </c>
       <c r="G6" t="n">
         <v>51.47</v>
       </c>
       <c r="H6" t="n">
-        <v>-16.96</v>
+        <v>-15.7</v>
       </c>
       <c r="I6" t="n">
-        <v>258959.88</v>
+        <v>260225.71</v>
       </c>
       <c r="J6" t="n">
-        <v>1963193.89</v>
+        <v>1964459.72</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>66.67</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="F7" t="n">
-        <v>33.47</v>
+        <v>33.55</v>
       </c>
       <c r="G7" t="n">
         <v>64.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-47.88</v>
+        <v>-47.93</v>
       </c>
       <c r="I7" t="n">
-        <v>280948.09</v>
+        <v>277932.54</v>
       </c>
       <c r="J7" t="n">
-        <v>2244141.98</v>
+        <v>2242392.26</v>
       </c>
     </row>
     <row r="8">
@@ -703,19 +703,19 @@
         <v>6.56</v>
       </c>
       <c r="F8" t="n">
-        <v>17.13</v>
+        <v>17.18</v>
       </c>
       <c r="G8" t="n">
         <v>45.88</v>
       </c>
       <c r="H8" t="n">
-        <v>-59.35</v>
+        <v>-59.08</v>
       </c>
       <c r="I8" t="n">
-        <v>294964</v>
+        <v>294984.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2539105.98</v>
+        <v>2537376.76</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         <v>55.81</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.91</v>
+        <v>-2.32</v>
       </c>
       <c r="F9" t="n">
-        <v>26.6</v>
+        <v>26.72</v>
       </c>
       <c r="G9" t="n">
         <v>20.59</v>
       </c>
       <c r="H9" t="n">
-        <v>-44.4</v>
+        <v>-44.79</v>
       </c>
       <c r="I9" t="n">
-        <v>-82347.27</v>
+        <v>-99669.63</v>
       </c>
       <c r="J9" t="n">
-        <v>2456758.71</v>
+        <v>2437707.13</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         <v>53.85</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.14</v>
+        <v>-3.19</v>
       </c>
       <c r="F10" t="n">
-        <v>22.92</v>
+        <v>23.08</v>
       </c>
       <c r="G10" t="n">
         <v>27.79</v>
       </c>
       <c r="H10" t="n">
-        <v>-48.11</v>
+        <v>-48.48</v>
       </c>
       <c r="I10" t="n">
-        <v>-40810</v>
+        <v>-41475.75</v>
       </c>
       <c r="J10" t="n">
-        <v>2415948.71</v>
+        <v>2396231.38</v>
       </c>
     </row>
     <row r="11">
@@ -802,22 +802,22 @@
         <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="F11" t="n">
-        <v>19.49</v>
+        <v>19.6</v>
       </c>
       <c r="G11" t="n">
         <v>33.25</v>
       </c>
       <c r="H11" t="n">
-        <v>-51.29</v>
+        <v>-51.88</v>
       </c>
       <c r="I11" t="n">
-        <v>63213.76</v>
+        <v>53544.92</v>
       </c>
       <c r="J11" t="n">
-        <v>2479162.47</v>
+        <v>2449776.3</v>
       </c>
     </row>
     <row r="12">
@@ -833,25 +833,25 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.04</v>
+        <v>5.13</v>
       </c>
       <c r="F12" t="n">
-        <v>15.03</v>
+        <v>15.12</v>
       </c>
       <c r="G12" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-49.83</v>
+        <v>-47.04</v>
       </c>
       <c r="I12" t="n">
-        <v>171486.29</v>
+        <v>174564.02</v>
       </c>
       <c r="J12" t="n">
-        <v>2650648.76</v>
+        <v>2624340.32</v>
       </c>
     </row>
     <row r="13">
@@ -870,22 +870,22 @@
         <v>77.27</v>
       </c>
       <c r="E13" t="n">
-        <v>5.05</v>
+        <v>5.01</v>
       </c>
       <c r="F13" t="n">
-        <v>8.59</v>
+        <v>8.68</v>
       </c>
       <c r="G13" t="n">
         <v>34</v>
       </c>
       <c r="H13" t="n">
-        <v>-22.65</v>
+        <v>-23.51</v>
       </c>
       <c r="I13" t="n">
-        <v>111044.34</v>
+        <v>110182.27</v>
       </c>
       <c r="J13" t="n">
-        <v>2761693.1</v>
+        <v>2734522.59</v>
       </c>
     </row>
   </sheetData>

--- a/result/月度汇总.xlsx
+++ b/result/月度汇总.xlsx
@@ -493,25 +493,25 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>57.69</v>
+        <v>73.08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.89</v>
+        <v>5.13</v>
       </c>
       <c r="F2" t="n">
-        <v>10.62</v>
+        <v>17.42</v>
       </c>
       <c r="G2" t="n">
-        <v>18.35</v>
+        <v>65.02</v>
       </c>
       <c r="H2" t="n">
         <v>-19.77</v>
       </c>
       <c r="I2" t="n">
-        <v>49060.12</v>
+        <v>133320.91</v>
       </c>
       <c r="J2" t="n">
-        <v>549060.12</v>
+        <v>633320.91</v>
       </c>
     </row>
     <row r="3">
@@ -530,22 +530,22 @@
         <v>72.73</v>
       </c>
       <c r="E3" t="n">
-        <v>6.44</v>
+        <v>7.27</v>
       </c>
       <c r="F3" t="n">
-        <v>21.3</v>
+        <v>24.73</v>
       </c>
       <c r="G3" t="n">
-        <v>54.43</v>
+        <v>59.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.17</v>
+        <v>-14.91</v>
       </c>
       <c r="I3" t="n">
-        <v>283248.92</v>
+        <v>319804.03</v>
       </c>
       <c r="J3" t="n">
-        <v>832309.04</v>
+        <v>953124.9399999999</v>
       </c>
     </row>
     <row r="4">
@@ -561,25 +561,25 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>70.77</v>
+        <v>69.23</v>
       </c>
       <c r="E4" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="F4" t="n">
-        <v>18.83</v>
+        <v>22.15</v>
       </c>
       <c r="G4" t="n">
-        <v>30.48</v>
+        <v>59.7</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.36</v>
+        <v>-13.86</v>
       </c>
       <c r="I4" t="n">
-        <v>303499.76</v>
+        <v>297151.75</v>
       </c>
       <c r="J4" t="n">
-        <v>1135808.8</v>
+        <v>1250276.69</v>
       </c>
     </row>
     <row r="5">
@@ -595,13 +595,13 @@
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>77.61</v>
+        <v>76.12</v>
       </c>
       <c r="E5" t="n">
-        <v>8.48</v>
+        <v>10.98</v>
       </c>
       <c r="F5" t="n">
-        <v>16.1</v>
+        <v>21.76</v>
       </c>
       <c r="G5" t="n">
         <v>196.3</v>
@@ -610,10 +610,10 @@
         <v>-14.07</v>
       </c>
       <c r="I5" t="n">
-        <v>568425.21</v>
+        <v>735435.71</v>
       </c>
       <c r="J5" t="n">
-        <v>1704234.01</v>
+        <v>1985712.4</v>
       </c>
     </row>
     <row r="6">
@@ -629,25 +629,25 @@
         <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>71.67</v>
+        <v>76.67</v>
       </c>
       <c r="E6" t="n">
-        <v>4.34</v>
+        <v>6.83</v>
       </c>
       <c r="F6" t="n">
-        <v>26.23</v>
+        <v>29.73</v>
       </c>
       <c r="G6" t="n">
-        <v>51.47</v>
+        <v>108.09</v>
       </c>
       <c r="H6" t="n">
         <v>-15.7</v>
       </c>
       <c r="I6" t="n">
-        <v>260225.71</v>
+        <v>409674.27</v>
       </c>
       <c r="J6" t="n">
-        <v>1964459.72</v>
+        <v>2395386.67</v>
       </c>
     </row>
     <row r="7">
@@ -663,25 +663,25 @@
         <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>66.67</v>
+        <v>67.95</v>
       </c>
       <c r="E7" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="F7" t="n">
-        <v>33.55</v>
+        <v>34.69</v>
       </c>
       <c r="G7" t="n">
-        <v>64.3</v>
+        <v>108.09</v>
       </c>
       <c r="H7" t="n">
         <v>-47.93</v>
       </c>
       <c r="I7" t="n">
-        <v>277932.54</v>
+        <v>327480.92</v>
       </c>
       <c r="J7" t="n">
-        <v>2242392.26</v>
+        <v>2722867.59</v>
       </c>
     </row>
     <row r="8">
@@ -697,13 +697,13 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>86.67</v>
+        <v>84.44</v>
       </c>
       <c r="E8" t="n">
-        <v>6.56</v>
+        <v>6.02</v>
       </c>
       <c r="F8" t="n">
-        <v>17.18</v>
+        <v>18.07</v>
       </c>
       <c r="G8" t="n">
         <v>45.88</v>
@@ -712,10 +712,10 @@
         <v>-59.08</v>
       </c>
       <c r="I8" t="n">
-        <v>294984.5</v>
+        <v>271040.19</v>
       </c>
       <c r="J8" t="n">
-        <v>2537376.76</v>
+        <v>2993907.78</v>
       </c>
     </row>
     <row r="9">
@@ -731,13 +731,13 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>55.81</v>
+        <v>53.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.32</v>
+        <v>-3.19</v>
       </c>
       <c r="F9" t="n">
-        <v>26.72</v>
+        <v>28.12</v>
       </c>
       <c r="G9" t="n">
         <v>20.59</v>
@@ -746,10 +746,10 @@
         <v>-44.79</v>
       </c>
       <c r="I9" t="n">
-        <v>-99669.63</v>
+        <v>-137256.47</v>
       </c>
       <c r="J9" t="n">
-        <v>2437707.13</v>
+        <v>2856651.31</v>
       </c>
     </row>
     <row r="10">
@@ -765,25 +765,25 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>53.85</v>
+        <v>46.15</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.19</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>23.08</v>
+        <v>29.85</v>
       </c>
       <c r="G10" t="n">
-        <v>27.79</v>
+        <v>46.78</v>
       </c>
       <c r="H10" t="n">
         <v>-48.48</v>
       </c>
       <c r="I10" t="n">
-        <v>-41475.75</v>
+        <v>-12232.21</v>
       </c>
       <c r="J10" t="n">
-        <v>2396231.38</v>
+        <v>2844419.1</v>
       </c>
     </row>
     <row r="11">
@@ -802,22 +802,22 @@
         <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>0.71</v>
+        <v>1.7</v>
       </c>
       <c r="F11" t="n">
-        <v>19.6</v>
+        <v>21.39</v>
       </c>
       <c r="G11" t="n">
-        <v>33.25</v>
+        <v>54.9</v>
       </c>
       <c r="H11" t="n">
         <v>-51.88</v>
       </c>
       <c r="I11" t="n">
-        <v>53544.92</v>
+        <v>127799.76</v>
       </c>
       <c r="J11" t="n">
-        <v>2449776.3</v>
+        <v>2972218.86</v>
       </c>
     </row>
     <row r="12">
@@ -833,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>85.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.13</v>
+        <v>5.36</v>
       </c>
       <c r="F12" t="n">
-        <v>15.12</v>
+        <v>17.41</v>
       </c>
       <c r="G12" t="n">
         <v>69.70999999999999</v>
@@ -848,10 +848,10 @@
         <v>-47.04</v>
       </c>
       <c r="I12" t="n">
-        <v>174564.02</v>
+        <v>182075.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2624340.32</v>
+        <v>3154294.46</v>
       </c>
     </row>
     <row r="13">
@@ -870,22 +870,22 @@
         <v>77.27</v>
       </c>
       <c r="E13" t="n">
-        <v>5.01</v>
+        <v>3.63</v>
       </c>
       <c r="F13" t="n">
-        <v>8.68</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>34</v>
+        <v>23.82</v>
       </c>
       <c r="H13" t="n">
         <v>-23.51</v>
       </c>
       <c r="I13" t="n">
-        <v>110182.27</v>
+        <v>79914.61</v>
       </c>
       <c r="J13" t="n">
-        <v>2734522.59</v>
+        <v>3234209.07</v>
       </c>
     </row>
   </sheetData>

--- a/result/月度汇总.xlsx
+++ b/result/月度汇总.xlsx
@@ -632,22 +632,22 @@
         <v>76.67</v>
       </c>
       <c r="E6" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="n">
-        <v>29.73</v>
+        <v>29.75</v>
       </c>
       <c r="G6" t="n">
         <v>108.09</v>
       </c>
       <c r="H6" t="n">
-        <v>-15.7</v>
+        <v>-17.22</v>
       </c>
       <c r="I6" t="n">
-        <v>409674.27</v>
+        <v>408155.28</v>
       </c>
       <c r="J6" t="n">
-        <v>2395386.67</v>
+        <v>2393867.68</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>67.95</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="F7" t="n">
-        <v>34.69</v>
+        <v>34.77</v>
       </c>
       <c r="G7" t="n">
         <v>108.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-47.93</v>
+        <v>-47.47</v>
       </c>
       <c r="I7" t="n">
-        <v>327480.92</v>
+        <v>323459.01</v>
       </c>
       <c r="J7" t="n">
-        <v>2722867.59</v>
+        <v>2717326.69</v>
       </c>
     </row>
     <row r="8">
@@ -700,22 +700,22 @@
         <v>84.44</v>
       </c>
       <c r="E8" t="n">
-        <v>6.02</v>
+        <v>5.93</v>
       </c>
       <c r="F8" t="n">
-        <v>18.07</v>
+        <v>18.11</v>
       </c>
       <c r="G8" t="n">
         <v>45.88</v>
       </c>
       <c r="H8" t="n">
-        <v>-59.08</v>
+        <v>-61.2</v>
       </c>
       <c r="I8" t="n">
-        <v>271040.19</v>
+        <v>266971.38</v>
       </c>
       <c r="J8" t="n">
-        <v>2993907.78</v>
+        <v>2984298.07</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         <v>53.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.19</v>
+        <v>-3.43</v>
       </c>
       <c r="F9" t="n">
-        <v>28.12</v>
+        <v>28.23</v>
       </c>
       <c r="G9" t="n">
         <v>20.59</v>
       </c>
       <c r="H9" t="n">
-        <v>-44.79</v>
+        <v>-46.72</v>
       </c>
       <c r="I9" t="n">
-        <v>-137256.47</v>
+        <v>-147281.63</v>
       </c>
       <c r="J9" t="n">
-        <v>2856651.31</v>
+        <v>2837016.44</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         <v>46.15</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="F10" t="n">
-        <v>29.85</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>46.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-48.48</v>
+        <v>-49.59</v>
       </c>
       <c r="I10" t="n">
-        <v>-12232.21</v>
+        <v>-14450.37</v>
       </c>
       <c r="J10" t="n">
-        <v>2844419.1</v>
+        <v>2822566.07</v>
       </c>
     </row>
     <row r="11">
@@ -802,22 +802,22 @@
         <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="F11" t="n">
-        <v>21.39</v>
+        <v>21.49</v>
       </c>
       <c r="G11" t="n">
         <v>54.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-51.88</v>
+        <v>-52.7</v>
       </c>
       <c r="I11" t="n">
-        <v>127799.76</v>
+        <v>129361.54</v>
       </c>
       <c r="J11" t="n">
-        <v>2972218.86</v>
+        <v>2951927.61</v>
       </c>
     </row>
     <row r="12">
@@ -836,22 +836,22 @@
         <v>82.34999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.36</v>
+        <v>5.52</v>
       </c>
       <c r="F12" t="n">
-        <v>17.41</v>
+        <v>17.5</v>
       </c>
       <c r="G12" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-47.04</v>
+        <v>-48.03</v>
       </c>
       <c r="I12" t="n">
-        <v>182075.6</v>
+        <v>187527.11</v>
       </c>
       <c r="J12" t="n">
-        <v>3154294.46</v>
+        <v>3139454.72</v>
       </c>
     </row>
     <row r="13">
@@ -870,22 +870,22 @@
         <v>77.27</v>
       </c>
       <c r="E13" t="n">
-        <v>3.63</v>
+        <v>3.39</v>
       </c>
       <c r="F13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G13" t="n">
         <v>23.82</v>
       </c>
       <c r="H13" t="n">
-        <v>-23.51</v>
+        <v>-26.72</v>
       </c>
       <c r="I13" t="n">
-        <v>79914.61</v>
+        <v>74529.67</v>
       </c>
       <c r="J13" t="n">
-        <v>3234209.07</v>
+        <v>3213984.39</v>
       </c>
     </row>
   </sheetData>

--- a/result/月度汇总.xlsx
+++ b/result/月度汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,22 +632,22 @@
         <v>76.67</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
       <c r="F6" t="n">
-        <v>29.75</v>
+        <v>29.78</v>
       </c>
       <c r="G6" t="n">
         <v>108.09</v>
       </c>
       <c r="H6" t="n">
-        <v>-17.22</v>
+        <v>-19.75</v>
       </c>
       <c r="I6" t="n">
-        <v>408155.28</v>
+        <v>405623.63</v>
       </c>
       <c r="J6" t="n">
-        <v>2393867.68</v>
+        <v>2391336.03</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>67.95</v>
       </c>
       <c r="E7" t="n">
-        <v>4.15</v>
+        <v>3.84</v>
       </c>
       <c r="F7" t="n">
-        <v>34.77</v>
+        <v>34.92</v>
       </c>
       <c r="G7" t="n">
         <v>108.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-47.47</v>
+        <v>-51.66</v>
       </c>
       <c r="I7" t="n">
-        <v>323459.01</v>
+        <v>299195.69</v>
       </c>
       <c r="J7" t="n">
-        <v>2717326.69</v>
+        <v>2690531.72</v>
       </c>
     </row>
     <row r="8">
@@ -700,22 +700,22 @@
         <v>84.44</v>
       </c>
       <c r="E8" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="F8" t="n">
-        <v>18.11</v>
+        <v>18.2</v>
       </c>
       <c r="G8" t="n">
         <v>45.88</v>
       </c>
       <c r="H8" t="n">
-        <v>-61.2</v>
+        <v>-62.26</v>
       </c>
       <c r="I8" t="n">
-        <v>266971.38</v>
+        <v>264143.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2984298.07</v>
+        <v>2954675.52</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         <v>53.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.43</v>
+        <v>-3.42</v>
       </c>
       <c r="F9" t="n">
-        <v>28.23</v>
+        <v>28.47</v>
       </c>
       <c r="G9" t="n">
         <v>20.59</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.72</v>
+        <v>-49.42</v>
       </c>
       <c r="I9" t="n">
-        <v>-147281.63</v>
+        <v>-147263.44</v>
       </c>
       <c r="J9" t="n">
-        <v>2837016.44</v>
+        <v>2807412.08</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         <v>46.15</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.11</v>
+        <v>-1.66</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>30.31</v>
       </c>
       <c r="G10" t="n">
         <v>46.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-49.59</v>
+        <v>-53.6</v>
       </c>
       <c r="I10" t="n">
-        <v>-14450.37</v>
+        <v>-21552.05</v>
       </c>
       <c r="J10" t="n">
-        <v>2822566.07</v>
+        <v>2785860.03</v>
       </c>
     </row>
     <row r="11">
@@ -802,22 +802,22 @@
         <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="F11" t="n">
-        <v>21.49</v>
+        <v>21.71</v>
       </c>
       <c r="G11" t="n">
         <v>54.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-52.7</v>
+        <v>-55.63</v>
       </c>
       <c r="I11" t="n">
-        <v>129361.54</v>
+        <v>113919.47</v>
       </c>
       <c r="J11" t="n">
-        <v>2951927.61</v>
+        <v>2899779.5</v>
       </c>
     </row>
     <row r="12">
@@ -836,22 +836,22 @@
         <v>82.34999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.52</v>
+        <v>5.49</v>
       </c>
       <c r="F12" t="n">
-        <v>17.5</v>
+        <v>17.62</v>
       </c>
       <c r="G12" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-48.03</v>
+        <v>-50.38</v>
       </c>
       <c r="I12" t="n">
-        <v>187527.11</v>
+        <v>186717.69</v>
       </c>
       <c r="J12" t="n">
-        <v>3139454.72</v>
+        <v>3086497.19</v>
       </c>
     </row>
     <row r="13">
@@ -870,22 +870,56 @@
         <v>77.27</v>
       </c>
       <c r="E13" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="F13" t="n">
-        <v>9.73</v>
+        <v>9.91</v>
       </c>
       <c r="G13" t="n">
         <v>23.82</v>
       </c>
       <c r="H13" t="n">
-        <v>-26.72</v>
+        <v>-30.17</v>
       </c>
       <c r="I13" t="n">
-        <v>74529.67</v>
+        <v>68909.63</v>
       </c>
       <c r="J13" t="n">
-        <v>3213984.39</v>
+        <v>3155406.82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Table202606</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-32.33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>105939.44</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3261346.26</v>
       </c>
     </row>
   </sheetData>

--- a/result/月度汇总.xlsx
+++ b/result/月度汇总.xlsx
@@ -632,22 +632,22 @@
         <v>76.67</v>
       </c>
       <c r="E6" t="n">
-        <v>6.76</v>
+        <v>6.74</v>
       </c>
       <c r="F6" t="n">
-        <v>29.78</v>
+        <v>29.85</v>
       </c>
       <c r="G6" t="n">
         <v>108.09</v>
       </c>
       <c r="H6" t="n">
-        <v>-19.75</v>
+        <v>-20.76</v>
       </c>
       <c r="I6" t="n">
-        <v>405623.63</v>
+        <v>404610.98</v>
       </c>
       <c r="J6" t="n">
-        <v>2391336.03</v>
+        <v>2390323.38</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>67.95</v>
       </c>
       <c r="E7" t="n">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="F7" t="n">
-        <v>34.92</v>
+        <v>35.23</v>
       </c>
       <c r="G7" t="n">
         <v>108.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-51.66</v>
+        <v>-53.03</v>
       </c>
       <c r="I7" t="n">
-        <v>299195.69</v>
+        <v>282133.55</v>
       </c>
       <c r="J7" t="n">
-        <v>2690531.72</v>
+        <v>2672456.93</v>
       </c>
     </row>
     <row r="8">
@@ -700,10 +700,10 @@
         <v>84.44</v>
       </c>
       <c r="E8" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="F8" t="n">
-        <v>18.2</v>
+        <v>18.38</v>
       </c>
       <c r="G8" t="n">
         <v>45.88</v>
@@ -712,10 +712,10 @@
         <v>-62.26</v>
       </c>
       <c r="I8" t="n">
-        <v>264143.8</v>
+        <v>263472.66</v>
       </c>
       <c r="J8" t="n">
-        <v>2954675.52</v>
+        <v>2935929.59</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         <v>53.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.42</v>
+        <v>-3.49</v>
       </c>
       <c r="F9" t="n">
-        <v>28.47</v>
+        <v>28.93</v>
       </c>
       <c r="G9" t="n">
         <v>20.59</v>
       </c>
       <c r="H9" t="n">
-        <v>-49.42</v>
+        <v>-49.23</v>
       </c>
       <c r="I9" t="n">
-        <v>-147263.44</v>
+        <v>-150019.67</v>
       </c>
       <c r="J9" t="n">
-        <v>2807412.08</v>
+        <v>2785909.92</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         <v>46.15</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.66</v>
+        <v>-1.74</v>
       </c>
       <c r="F10" t="n">
-        <v>30.31</v>
+        <v>30.92</v>
       </c>
       <c r="G10" t="n">
         <v>46.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-53.6</v>
+        <v>-54.12</v>
       </c>
       <c r="I10" t="n">
-        <v>-21552.05</v>
+        <v>-22587.19</v>
       </c>
       <c r="J10" t="n">
-        <v>2785860.03</v>
+        <v>2763322.73</v>
       </c>
     </row>
     <row r="11">
@@ -799,25 +799,25 @@
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>69.33</v>
       </c>
       <c r="E11" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="F11" t="n">
-        <v>21.71</v>
+        <v>22.13</v>
       </c>
       <c r="G11" t="n">
         <v>54.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-55.63</v>
+        <v>-55.16</v>
       </c>
       <c r="I11" t="n">
-        <v>113919.47</v>
+        <v>118603.02</v>
       </c>
       <c r="J11" t="n">
-        <v>2899779.5</v>
+        <v>2881925.75</v>
       </c>
     </row>
     <row r="12">
@@ -836,22 +836,22 @@
         <v>82.34999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.49</v>
+        <v>5.57</v>
       </c>
       <c r="F12" t="n">
-        <v>17.62</v>
+        <v>17.85</v>
       </c>
       <c r="G12" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-50.38</v>
+        <v>-47.25</v>
       </c>
       <c r="I12" t="n">
-        <v>186717.69</v>
+        <v>189255.19</v>
       </c>
       <c r="J12" t="n">
-        <v>3086497.19</v>
+        <v>3071180.94</v>
       </c>
     </row>
     <row r="13">
@@ -870,56 +870,56 @@
         <v>77.27</v>
       </c>
       <c r="E13" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="F13" t="n">
-        <v>9.91</v>
+        <v>10.27</v>
       </c>
       <c r="G13" t="n">
         <v>23.82</v>
       </c>
       <c r="H13" t="n">
-        <v>-30.17</v>
+        <v>-31.43</v>
       </c>
       <c r="I13" t="n">
-        <v>68909.63</v>
+        <v>72591.55</v>
       </c>
       <c r="J13" t="n">
-        <v>3155406.82</v>
+        <v>3143772.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Table202606</t>
+          <t>Table260606无牛气度</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>85</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>7.85</v>
+        <v>9.23</v>
       </c>
       <c r="G14" t="n">
-        <v>23.3</v>
+        <v>20.34</v>
       </c>
       <c r="H14" t="n">
-        <v>-32.33</v>
+        <v>-33.49</v>
       </c>
       <c r="I14" t="n">
-        <v>105939.44</v>
+        <v>27870.94</v>
       </c>
       <c r="J14" t="n">
-        <v>3261346.26</v>
+        <v>3171643.43</v>
       </c>
     </row>
   </sheetData>
